--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,27 +434,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -466,32 +451,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.78976</v>
+        <v>16.65911</v>
       </c>
       <c r="D2" t="n">
-        <v>16.78438</v>
+        <v>15.97555</v>
       </c>
       <c r="E2" t="n">
-        <v>16.50977</v>
+        <v>16.18002</v>
       </c>
       <c r="F2" t="n">
-        <v>55.09643</v>
+        <v>21.74502</v>
       </c>
       <c r="G2" t="n">
-        <v>43.27747</v>
-      </c>
-      <c r="H2" t="n">
-        <v>85.9652</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.05106</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.80691</v>
+        <v>35.02737</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +477,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.23018</v>
+        <v>16.94679</v>
       </c>
       <c r="D3" t="n">
-        <v>16.48593</v>
+        <v>16.1082</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81022</v>
+        <v>16.22272</v>
       </c>
       <c r="F3" t="n">
-        <v>55.51063</v>
+        <v>21.61177</v>
       </c>
       <c r="G3" t="n">
-        <v>42.20341</v>
-      </c>
-      <c r="H3" t="n">
-        <v>87.26886</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.04961</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.81852</v>
+        <v>34.48939</v>
       </c>
     </row>
     <row r="4">
@@ -532,28 +499,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.35857</v>
+        <v>16.43164</v>
       </c>
       <c r="D4" t="n">
-        <v>16.66795</v>
+        <v>16.09969</v>
       </c>
       <c r="E4" t="n">
-        <v>16.61986</v>
+        <v>16.2523</v>
       </c>
       <c r="F4" t="n">
-        <v>55.18178</v>
+        <v>21.86968</v>
       </c>
       <c r="G4" t="n">
-        <v>43.18292</v>
-      </c>
-      <c r="H4" t="n">
-        <v>85.53493</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05109</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.84963</v>
+        <v>34.04499</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +521,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.95808</v>
+        <v>16.88431</v>
       </c>
       <c r="D5" t="n">
-        <v>16.48846</v>
+        <v>15.96979</v>
       </c>
       <c r="E5" t="n">
-        <v>16.88487</v>
+        <v>16.59542</v>
       </c>
       <c r="F5" t="n">
-        <v>55.24286</v>
+        <v>21.72784</v>
       </c>
       <c r="G5" t="n">
-        <v>42.4045</v>
-      </c>
-      <c r="H5" t="n">
-        <v>85.25754000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05133</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.81986</v>
+        <v>33.74145</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +543,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.45132</v>
+        <v>16.59227</v>
       </c>
       <c r="D6" t="n">
-        <v>16.37883</v>
+        <v>16.17431</v>
       </c>
       <c r="E6" t="n">
-        <v>16.9717</v>
+        <v>16.23442</v>
       </c>
       <c r="F6" t="n">
-        <v>54.65719</v>
+        <v>21.92718</v>
       </c>
       <c r="G6" t="n">
-        <v>43.05729</v>
-      </c>
-      <c r="H6" t="n">
-        <v>84.24181</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.05113</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.81151</v>
+        <v>34.59329</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +565,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.64015</v>
+        <v>16.87784</v>
       </c>
       <c r="D7" t="n">
-        <v>16.71186</v>
+        <v>15.9358</v>
       </c>
       <c r="E7" t="n">
-        <v>16.38176</v>
+        <v>16.41917</v>
       </c>
       <c r="F7" t="n">
-        <v>56.09926</v>
+        <v>21.83119</v>
       </c>
       <c r="G7" t="n">
-        <v>42.36669</v>
-      </c>
-      <c r="H7" t="n">
-        <v>84.72984</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.05088</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.77877</v>
+        <v>34.17889</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +587,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.78939</v>
+        <v>16.60288</v>
       </c>
       <c r="D8" t="n">
-        <v>16.60701</v>
+        <v>16.37474</v>
       </c>
       <c r="E8" t="n">
-        <v>16.92404</v>
+        <v>16.57328</v>
       </c>
       <c r="F8" t="n">
-        <v>56.01303</v>
+        <v>21.65912</v>
       </c>
       <c r="G8" t="n">
-        <v>42.4076</v>
-      </c>
-      <c r="H8" t="n">
-        <v>84.9598</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.05093</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.81935</v>
+        <v>35.04869</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +609,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.85195</v>
+        <v>16.76494</v>
       </c>
       <c r="D9" t="n">
-        <v>16.66862</v>
+        <v>16.34591</v>
       </c>
       <c r="E9" t="n">
-        <v>16.66314</v>
+        <v>16.40741</v>
       </c>
       <c r="F9" t="n">
-        <v>54.74548</v>
+        <v>21.60883</v>
       </c>
       <c r="G9" t="n">
-        <v>42.27309</v>
-      </c>
-      <c r="H9" t="n">
-        <v>85.50988</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.05068</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.83106</v>
+        <v>34.67226</v>
       </c>
     </row>
     <row r="10">
@@ -718,28 +631,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.84708</v>
+        <v>16.8297</v>
       </c>
       <c r="D10" t="n">
-        <v>16.48712</v>
+        <v>16.04758</v>
       </c>
       <c r="E10" t="n">
-        <v>16.33096</v>
+        <v>16.30408</v>
       </c>
       <c r="F10" t="n">
-        <v>55.43911</v>
+        <v>21.70794</v>
       </c>
       <c r="G10" t="n">
-        <v>43.07659</v>
-      </c>
-      <c r="H10" t="n">
-        <v>84.60705</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.04977</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.8233</v>
+        <v>33.97244</v>
       </c>
     </row>
     <row r="11">
@@ -760,25 +664,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -792,32 +686,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 2</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.99852</v>
+        <v>16.65123</v>
       </c>
       <c r="D12" t="n">
-        <v>16.49432</v>
+        <v>16.12482</v>
       </c>
       <c r="E12" t="n">
-        <v>16.63684</v>
+        <v>16.57938</v>
       </c>
       <c r="F12" t="n">
-        <v>55.90914</v>
+        <v>42.55643</v>
       </c>
       <c r="G12" t="n">
-        <v>41.98237</v>
+        <v>0.04988</v>
       </c>
       <c r="H12" t="n">
-        <v>85.72823</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.05046</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.83869</v>
+        <v>1.84702</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +715,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.71276</v>
+        <v>16.96731</v>
       </c>
       <c r="D13" t="n">
-        <v>16.89472</v>
+        <v>16.33063</v>
       </c>
       <c r="E13" t="n">
-        <v>16.6323</v>
+        <v>16.52234</v>
       </c>
       <c r="F13" t="n">
-        <v>55.57842</v>
+        <v>43.00189</v>
       </c>
       <c r="G13" t="n">
-        <v>43.11031</v>
+        <v>0.05013</v>
       </c>
       <c r="H13" t="n">
-        <v>86.04369</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05168</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.8543</v>
+        <v>1.78786</v>
       </c>
     </row>
     <row r="14">
@@ -858,28 +740,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.94915</v>
+        <v>16.68496</v>
       </c>
       <c r="D14" t="n">
-        <v>16.1551</v>
+        <v>16.61195</v>
       </c>
       <c r="E14" t="n">
-        <v>16.67931</v>
+        <v>16.62036</v>
       </c>
       <c r="F14" t="n">
-        <v>56.52514</v>
+        <v>42.72298</v>
       </c>
       <c r="G14" t="n">
-        <v>42.31896</v>
+        <v>0.05103</v>
       </c>
       <c r="H14" t="n">
-        <v>86.22653</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.05003</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.83779</v>
+        <v>1.81677</v>
       </c>
     </row>
     <row r="15">
@@ -889,28 +765,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.81856</v>
+        <v>17.22975</v>
       </c>
       <c r="D15" t="n">
-        <v>16.81765</v>
+        <v>16.47461</v>
       </c>
       <c r="E15" t="n">
-        <v>16.61568</v>
+        <v>16.59937</v>
       </c>
       <c r="F15" t="n">
-        <v>56.7297</v>
+        <v>42.19781</v>
       </c>
       <c r="G15" t="n">
-        <v>42.77609</v>
+        <v>0.05087</v>
       </c>
       <c r="H15" t="n">
-        <v>85.05388000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.04924</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.85013</v>
+        <v>1.82732</v>
       </c>
     </row>
     <row r="16">
@@ -920,28 +790,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.83161</v>
+        <v>16.94374</v>
       </c>
       <c r="D16" t="n">
-        <v>16.52651</v>
+        <v>16.74174</v>
       </c>
       <c r="E16" t="n">
-        <v>16.75802</v>
+        <v>16.74802</v>
       </c>
       <c r="F16" t="n">
-        <v>56.18788</v>
+        <v>41.77445</v>
       </c>
       <c r="G16" t="n">
-        <v>42.52284</v>
+        <v>0.05044</v>
       </c>
       <c r="H16" t="n">
-        <v>85.94913</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.04947</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.81585</v>
+        <v>1.80884</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +815,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.78548</v>
+        <v>16.90038</v>
       </c>
       <c r="D17" t="n">
-        <v>16.90166</v>
+        <v>16.65845</v>
       </c>
       <c r="E17" t="n">
-        <v>17.04993</v>
+        <v>16.74445</v>
       </c>
       <c r="F17" t="n">
-        <v>54.80501</v>
+        <v>42.33933</v>
       </c>
       <c r="G17" t="n">
-        <v>42.3114</v>
+        <v>0.04953</v>
       </c>
       <c r="H17" t="n">
-        <v>87.20766999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.04982</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.85049</v>
+        <v>1.85738</v>
       </c>
     </row>
     <row r="18">
@@ -982,28 +840,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.10736</v>
+        <v>16.93512</v>
       </c>
       <c r="D18" t="n">
-        <v>16.64077</v>
+        <v>16.47523</v>
       </c>
       <c r="E18" t="n">
-        <v>16.87262</v>
+        <v>16.84945</v>
       </c>
       <c r="F18" t="n">
-        <v>54.81715</v>
+        <v>41.96494</v>
       </c>
       <c r="G18" t="n">
-        <v>42.62006</v>
+        <v>0.05025</v>
       </c>
       <c r="H18" t="n">
-        <v>87.42214</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.04967</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.84274</v>
+        <v>1.81785</v>
       </c>
     </row>
     <row r="19">
@@ -1013,28 +865,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.58956</v>
+        <v>16.8069</v>
       </c>
       <c r="D19" t="n">
-        <v>16.78361</v>
+        <v>16.1865</v>
       </c>
       <c r="E19" t="n">
-        <v>16.55166</v>
+        <v>16.79805</v>
       </c>
       <c r="F19" t="n">
-        <v>55.05502</v>
+        <v>42.76353</v>
       </c>
       <c r="G19" t="n">
-        <v>41.46893</v>
+        <v>0.05089</v>
       </c>
       <c r="H19" t="n">
-        <v>84.86857000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.05072</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.7848</v>
+        <v>1.86816</v>
       </c>
     </row>
     <row r="20">
@@ -1044,258 +890,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.89975</v>
+        <v>16.68444</v>
       </c>
       <c r="D20" t="n">
-        <v>16.36467</v>
+        <v>16.56983</v>
       </c>
       <c r="E20" t="n">
-        <v>17.00037</v>
+        <v>16.58378</v>
       </c>
       <c r="F20" t="n">
-        <v>55.49246</v>
+        <v>43.28066</v>
       </c>
       <c r="G20" t="n">
-        <v>42.91957</v>
+        <v>0.0506</v>
       </c>
       <c r="H20" t="n">
-        <v>84.78592</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05063</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.86305</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>16.82329</v>
-      </c>
-      <c r="D22" t="n">
-        <v>15.83757</v>
-      </c>
-      <c r="E22" t="n">
-        <v>16.6121</v>
-      </c>
-      <c r="F22" t="n">
-        <v>21.35378</v>
-      </c>
-      <c r="G22" t="n">
-        <v>34.26276</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>16.34569</v>
-      </c>
-      <c r="D23" t="n">
-        <v>15.97234</v>
-      </c>
-      <c r="E23" t="n">
-        <v>16.39883</v>
-      </c>
-      <c r="F23" t="n">
-        <v>21.97522</v>
-      </c>
-      <c r="G23" t="n">
-        <v>34.58862</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>16.95677</v>
-      </c>
-      <c r="D24" t="n">
-        <v>16.35839</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16.37006</v>
-      </c>
-      <c r="F24" t="n">
-        <v>21.86154</v>
-      </c>
-      <c r="G24" t="n">
-        <v>33.95334</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>17.03759</v>
-      </c>
-      <c r="D25" t="n">
-        <v>15.91713</v>
-      </c>
-      <c r="E25" t="n">
-        <v>16.61527</v>
-      </c>
-      <c r="F25" t="n">
-        <v>21.93706</v>
-      </c>
-      <c r="G25" t="n">
-        <v>33.94511</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>16.69175</v>
-      </c>
-      <c r="D26" t="n">
-        <v>15.70375</v>
-      </c>
-      <c r="E26" t="n">
-        <v>16.0647</v>
-      </c>
-      <c r="F26" t="n">
-        <v>21.81424</v>
-      </c>
-      <c r="G26" t="n">
-        <v>34.41444</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>16.65171</v>
-      </c>
-      <c r="D27" t="n">
-        <v>15.70239</v>
-      </c>
-      <c r="E27" t="n">
-        <v>15.93684</v>
-      </c>
-      <c r="F27" t="n">
-        <v>21.81413</v>
-      </c>
-      <c r="G27" t="n">
-        <v>34.1686</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>16.90295</v>
-      </c>
-      <c r="D28" t="n">
-        <v>16.06261</v>
-      </c>
-      <c r="E28" t="n">
-        <v>16.56816</v>
-      </c>
-      <c r="F28" t="n">
-        <v>21.83984</v>
-      </c>
-      <c r="G28" t="n">
-        <v>34.5762</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>17.15646</v>
-      </c>
-      <c r="D29" t="n">
-        <v>15.85556</v>
-      </c>
-      <c r="E29" t="n">
-        <v>16.65968</v>
-      </c>
-      <c r="F29" t="n">
-        <v>21.50546</v>
-      </c>
-      <c r="G29" t="n">
-        <v>34.5623</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>16.41716</v>
-      </c>
-      <c r="D30" t="n">
-        <v>15.9175</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16.47995</v>
-      </c>
-      <c r="F30" t="n">
-        <v>21.88763</v>
-      </c>
-      <c r="G30" t="n">
-        <v>34.06166</v>
+        <v>1.83321</v>
       </c>
     </row>
   </sheetData>
